--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -12964,16 +12964,16 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -12964,16 +12964,16 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1061,9 +1058,6 @@
       <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.03537951651591013</v>
       </c>
@@ -1457,9 +1451,6 @@
       <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.02803464128485004</v>
       </c>
@@ -2741,9 +2732,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -2889,9 +2877,6 @@
       <c r="O15" t="n">
         <v>4</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.07075903303182025</v>
       </c>
@@ -3285,9 +3270,6 @@
       <c r="O17" t="n">
         <v>5</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.04672440214141673</v>
       </c>
@@ -4421,9 +4403,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4569,9 +4548,6 @@
       <c r="O25" t="n">
         <v>8</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.1415180660636405</v>
       </c>
@@ -4965,9 +4941,6 @@
       <c r="O27" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.02803464128485004</v>
       </c>
@@ -5953,9 +5926,6 @@
       <c r="O33" t="n">
         <v>47</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.1726221555174302</v>
       </c>
@@ -6101,9 +6071,6 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -6249,9 +6216,6 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -6645,9 +6609,6 @@
       <c r="O37" t="n">
         <v>4</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.03737952171313338</v>
       </c>
@@ -7633,9 +7594,6 @@
       <c r="O43" t="n">
         <v>14</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.05141936547327706</v>
       </c>
@@ -7781,9 +7739,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -7929,9 +7884,6 @@
       <c r="O45" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -8325,9 +8277,6 @@
       <c r="O47" t="n">
         <v>2</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -9313,9 +9262,6 @@
       <c r="O53" t="n">
         <v>10</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.002865038132769385</v>
       </c>
@@ -9461,9 +9407,6 @@
       <c r="O54" t="n">
         <v>16</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.05876498911231665</v>
       </c>
@@ -9609,9 +9552,6 @@
       <c r="O55" t="n">
         <v>3</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -9757,9 +9697,6 @@
       <c r="O56" t="n">
         <v>7</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.1238283078056854</v>
       </c>
@@ -10153,9 +10090,6 @@
       <c r="O58" t="n">
         <v>7</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.06541416299798342</v>
       </c>
@@ -10549,9 +10483,6 @@
       <c r="O60" t="n">
         <v>17</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.004870564825707955</v>
       </c>
@@ -10697,9 +10628,6 @@
       <c r="O61" t="n">
         <v>14</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.00401105338587714</v>
       </c>
@@ -10845,9 +10773,6 @@
       <c r="O62" t="n">
         <v>7</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.00200552669293857</v>
       </c>
@@ -10993,9 +10918,6 @@
       <c r="O63" t="n">
         <v>19</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.005443572452261832</v>
       </c>
@@ -11141,9 +11063,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -11289,9 +11208,6 @@
       <c r="O65" t="n">
         <v>3</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -11437,9 +11353,6 @@
       <c r="O66" t="n">
         <v>32</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.566072264254562</v>
       </c>
@@ -11828,16 +11741,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O68" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="R68" t="n">
-        <v>0.2990361737050671</v>
+        <v>0.2896912932767837</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -11990,10 +11900,10 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O69" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -12229,9 +12139,6 @@
       <c r="O70" t="n">
         <v>14</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.00401105338587714</v>
       </c>
@@ -12377,9 +12284,6 @@
       <c r="O71" t="n">
         <v>20</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.00573007626553877</v>
       </c>
@@ -12525,9 +12429,6 @@
       <c r="O72" t="n">
         <v>32</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.009168122024862033</v>
       </c>
@@ -12673,9 +12574,6 @@
       <c r="O73" t="n">
         <v>34</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.00974112965141591</v>
       </c>
@@ -12821,9 +12719,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -12969,9 +12864,6 @@
       <c r="O75" t="n">
         <v>3</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -13112,16 +13004,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -13274,10 +13163,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -13513,9 +13402,6 @@
       <c r="O78" t="n">
         <v>42</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.01203316015763142</v>
       </c>
@@ -13584,6 +13470,151 @@
         </is>
       </c>
       <c r="BC78" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>23</v>
+      </c>
+      <c r="O79" t="n">
+        <v>23</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.006589587705369587</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -13622,7 +13653,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -13705,7 +13736,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -13715,7 +13746,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -13767,7 +13798,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>576</v>
+        <v>601</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -13004,13 +13004,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O76" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R76" t="n">
-        <v>0.07075903303182025</v>
+        <v>0.1061385495477304</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -13163,10 +13163,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -13615,6 +13615,151 @@
         </is>
       </c>
       <c r="BC79" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>28</v>
+      </c>
+      <c r="O80" t="n">
+        <v>28</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.00802210677175428</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -13653,7 +13798,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13881,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -13746,7 +13891,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -13798,7 +13943,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>601</v>
+        <v>631</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -12859,13 +12859,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -13004,13 +13004,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O76" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R76" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -13163,10 +13163,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O77" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -13765,6 +13765,151 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>22</v>
+      </c>
+      <c r="O81" t="n">
+        <v>22</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.006303083892092647</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13798,7 +13943,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -13881,7 +14026,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -13891,7 +14036,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -13943,7 +14088,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>635</v>
+        <v>657</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -11203,13 +11203,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R65" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -12859,13 +12859,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O75" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R75" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -9508,12 +9508,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -9547,17 +9547,14 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0.005813909771376137</v>
+        <v>0</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -9586,42 +9583,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -9653,12 +9650,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -9692,95 +9689,78 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O56" t="n">
-        <v>7</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.1238283078056854</v>
+        <v>6</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -9807,17 +9787,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -9851,170 +9831,78 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O57" t="n">
-        <v>7</v>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>Vibrioinfeksjon</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD57" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG57" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP57" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV57" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10046,12 +9934,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -10085,95 +9973,78 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>7</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.06541416299798342</v>
+        <v>0</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10200,17 +10071,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -10244,170 +10115,78 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O59" t="n">
-        <v>7</v>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>Vibrioinfektion</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD59" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG59" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Vibrio category.</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP59" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
-        </is>
-      </c>
-      <c r="AT59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV59" t="inlineStr">
-        <is>
-          <t>fohm_sminet</t>
-        </is>
-      </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10439,12 +10218,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -10469,7 +10248,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -10478,13 +10257,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="O60" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="R60" t="n">
-        <v>0.004870564825707955</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -10517,42 +10296,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -10584,12 +10363,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -10614,7 +10393,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -10623,81 +10402,95 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O61" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R61" t="n">
-        <v>0.00401105338587714</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -10724,17 +10517,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -10759,7 +10552,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -10773,76 +10566,165 @@
       <c r="O62" t="n">
         <v>7</v>
       </c>
-      <c r="R62" t="n">
-        <v>0.00200552669293857</v>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Vibrioinfeksjon</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN62" t="b">
+        <v>1</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -10874,12 +10756,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -10904,7 +10786,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -10913,81 +10795,95 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="O63" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="R63" t="n">
-        <v>0.005443572452261832</v>
+        <v>0.06541416299798342</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11014,17 +10910,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -11049,90 +10945,179 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Vibrioinfektion</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Vibrio category.</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN64" t="b">
+        <v>1</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11164,12 +11149,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -11194,22 +11179,22 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="O65" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="R65" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.004870564825707955</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -11242,42 +11227,42 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11294,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -11339,104 +11324,90 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O66" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="R66" t="n">
-        <v>0.566072264254562</v>
+        <v>0.00401105338587714</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -11463,17 +11434,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -11498,179 +11469,90 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="O67" t="n">
-        <v>32</v>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>Vibrioinfeksjon</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN67" t="b">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.00200552669293857</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -11702,12 +11584,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -11732,104 +11614,90 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="O68" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="R68" t="n">
-        <v>0.2896912932767837</v>
+        <v>0.005443572452261832</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -11856,17 +11724,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -11900,170 +11768,81 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="O69" t="n">
-        <v>31</v>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>Vibrioinfektion</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD69" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.03305530637567811</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG69" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Vibrio category.</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN69" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP69" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
-        </is>
-      </c>
-      <c r="AT69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV69" t="inlineStr">
-        <is>
-          <t>fohm_sminet</t>
-        </is>
-      </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12095,12 +11874,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -12125,7 +11904,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -12134,17 +11913,14 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>14</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.00401105338587714</v>
+        <v>0</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -12173,42 +11949,42 @@
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12016,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -12270,7 +12046,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -12279,17 +12055,14 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>20</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0.00573007626553877</v>
+        <v>0</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -12318,42 +12091,42 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12385,12 +12158,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -12415,7 +12188,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -12424,17 +12197,14 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>32</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0.009168122024862033</v>
+        <v>0</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -12463,42 +12233,42 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12300,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -12560,7 +12330,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -12569,17 +12339,14 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>34</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0.00974112965141591</v>
+        <v>0</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -12608,42 +12375,42 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12442,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -12705,22 +12472,22 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -12753,42 +12520,42 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12820,12 +12587,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -12850,90 +12617,104 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="O75" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="R75" t="n">
-        <v>0.01356578946654432</v>
+        <v>0.566072264254562</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -12960,7 +12741,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -12995,37 +12776,112 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="O76" t="n">
-        <v>9</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0.1592078243215956</v>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>32</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>SER_NO_FHI_603_MONTHLY</t>
         </is>
       </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Vibrioinfeksjon</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN76" t="b">
+        <v>1</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -13119,17 +12975,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -13154,48 +13010,31 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="O77" t="n">
-        <v>9</v>
+        <v>31</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0.2896912932767837</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>Vibrioinfeksjon</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -13203,64 +13042,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD77" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG77" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN77" t="b">
-        <v>1</v>
-      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -13278,7 +13059,7 @@
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
         </is>
       </c>
       <c r="AT77" t="n">
@@ -13291,42 +13072,42 @@
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -13353,17 +13134,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -13388,90 +13169,179 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="O78" t="n">
-        <v>42</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0.01203316015763142</v>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Vibrioinfektion</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Vibrio category.</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN78" t="b">
+        <v>1</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -13533,22 +13403,22 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="O79" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="R79" t="n">
-        <v>0.006589587705369587</v>
+        <v>0.00401105338587714</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -13678,22 +13548,22 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="O80" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="R80" t="n">
-        <v>0.00802210677175428</v>
+        <v>0.00573007626553877</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -13823,22 +13693,22 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="O81" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="R81" t="n">
-        <v>0.006303083892092647</v>
+        <v>0.009168122024862033</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -13907,6 +13777,2952 @@
       <c r="BC81" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>34</v>
+      </c>
+      <c r="O82" t="n">
+        <v>34</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0.00974112965141591</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>9</v>
+      </c>
+      <c r="O83" t="n">
+        <v>9</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0.03305530637567811</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr"/>
+      <c r="AT84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
+      <c r="AT85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr"/>
+      <c r="AT86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>9</v>
+      </c>
+      <c r="O89" t="n">
+        <v>9</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0.01744172931412841</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>11</v>
+      </c>
+      <c r="O90" t="n">
+        <v>11</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0.1945873408375057</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>11</v>
+      </c>
+      <c r="O91" t="n">
+        <v>11</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Vibrioinfeksjon</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN91" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>42</v>
+      </c>
+      <c r="O92" t="n">
+        <v>42</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0.01203316015763142</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>23</v>
+      </c>
+      <c r="O93" t="n">
+        <v>23</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0.006589587705369587</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>28</v>
+      </c>
+      <c r="O94" t="n">
+        <v>28</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0.00802210677175428</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>22</v>
+      </c>
+      <c r="O95" t="n">
+        <v>22</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.006303083892092647</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>31</v>
+      </c>
+      <c r="O96" t="n">
+        <v>31</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0.008881618211585096</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Vibrioinfeksjon</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN100" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -13943,7 +16759,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -14026,7 +16842,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -14036,7 +16852,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -14056,7 +16872,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -14088,7 +16904,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>661</v>
+        <v>730</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -16255,13 +16255,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="16">
